--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484105_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484105_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5252</v>
+        <v>5.3512</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4393</v>
+        <v>3.7884</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0858</v>
+        <v>1.5628</v>
       </c>
       <c r="G2" t="n">
         <v>0.8663</v>
@@ -610,13 +610,13 @@
         <v>3.5709</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.278</v>
+        <v>-0.452</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6096</v>
+        <v>-0.2606</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6684</v>
+        <v>-0.1914</v>
       </c>
       <c r="V2" t="n">
         <v>3.5481</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6467</v>
+        <v>3.2855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8063</v>
+        <v>1.2767</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8404</v>
+        <v>2.0087</v>
       </c>
       <c r="G3" t="n">
         <v>0.183</v>
@@ -688,13 +688,13 @@
         <v>3.7693</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9963</v>
+        <v>-1.3575</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0031</v>
+        <v>-0.5327</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9932</v>
+        <v>-0.8249</v>
       </c>
       <c r="V3" t="n">
         <v>1.881</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8552</v>
+        <v>1.2174</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3715</v>
+        <v>0.6776</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4836</v>
+        <v>0.5397</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5199</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5816</v>
+        <v>0.9438</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3685</v>
+        <v>0.6746</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2131</v>
+        <v>0.2692</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1367</v>
+        <v>-0.0393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4062</v>
+        <v>0.2022</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2695</v>
+        <v>-0.2414</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4885</v>
@@ -844,13 +844,13 @@
         <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8236</v>
+        <v>0.6476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6292</v>
+        <v>0.4251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1944</v>
+        <v>0.2224</v>
       </c>
       <c r="V5" t="n">
         <v>0.6032</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1938</v>
+        <v>-0.2273</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1476</v>
+        <v>-1.125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9538</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2009</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0407</v>
+        <v>-1.0741</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.306</v>
+        <v>-0.2833</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7347</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1425</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2516</v>
+        <v>-0.8324</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2216</v>
+        <v>-1.6575</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9701</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2046</v>
+        <v>-0.0497</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.7993</v>
+        <v>0.8364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5948</v>
+        <v>-0.8861</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5813</v>
+        <v>0.0603</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9468</v>
+        <v>0.0202</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3655</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6232</v>
+        <v>-0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8525</v>
+        <v>0.8162</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.9263</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9838</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3887</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3725</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5724</v>
+        <v>0.3401</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4229</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1495</v>
+        <v>0.34</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3143</v>
+        <v>-1.3421</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4761</v>
+        <v>-2.9755</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1618</v>
+        <v>1.6334</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0497</v>
+        <v>-3.2046</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8364</v>
+        <v>-3.7993</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8861</v>
+        <v>0.5948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0603</v>
+        <v>-1.5813</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0202</v>
+        <v>-2.9468</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>1.3655</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.11</v>
+        <v>-1.6232</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8162</v>
+        <v>-0.8525</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9263</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P8" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.3887</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>3.3725</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8581</v>
+        <v>0.4818</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1814</v>
+        <v>0.669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6767</v>
+        <v>-0.1872</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3226</v>
+        <v>-3.7307</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2765</v>
+        <v>-2.9531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.954</v>
+        <v>-0.7775</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1569</v>
+        <v>-2.1652</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0454</v>
+        <v>-0.9474</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1115</v>
+        <v>-1.2178</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2518</v>
+        <v>-2.0406</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3321</v>
+        <v>-0.6802</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>-1.3604</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9051</v>
+        <v>-0.1247</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2867</v>
+        <v>-0.2672</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1918</v>
+        <v>0.1425</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.579</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1661</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1474</v>
+        <v>0.0297</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.0794</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4025</v>
+        <v>-0.0496</v>
       </c>
       <c r="V9" t="n">
-        <v>0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6745</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GOMES CORREIA</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6135</v>
+        <v>-3.9744</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1651</v>
+        <v>-4.9284</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5516</v>
+        <v>0.954</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.1569</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.0454</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5261</v>
+        <v>-1.1115</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8153</v>
+        <v>-0.2518</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1449</v>
+        <v>-0.3321</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9603</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.161</v>
+        <v>-0.9051</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5951</v>
+        <v>0.2867</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4341</v>
+        <v>-1.1918</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1903</v>
+        <v>-2.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1741</v>
+        <v>-4.1661</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4989</v>
+        <v>-0.102</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2011</v>
+        <v>-0.4025</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1469</v>
+        <v>0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6745</v>
+        <v>-0.4085</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4724</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>A. GOMES CORREIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.863</v>
+        <v>-4.0372</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2819</v>
+        <v>-4.4485</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.4113</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1652</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9474</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2178</v>
+        <v>-1.5261</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0406</v>
+        <v>-0.8153</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6802</v>
+        <v>1.1449</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3604</v>
+        <v>-1.9603</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1247</v>
+        <v>-0.161</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2672</v>
+        <v>-0.5951</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1425</v>
+        <v>0.4341</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1026</v>
+        <v>0.2763</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2494</v>
+        <v>0.2155</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1468</v>
+        <v>0.0608</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6032</v>
+        <v>-2.1469</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6032</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5082</v>
+        <v>-6.6387</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8413</v>
+        <v>-2.3085</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6669</v>
+        <v>-4.3302</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6881</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1925</v>
+        <v>-0.3231</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.255</v>
+        <v>0.2778</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9376</v>
+        <v>-0.6009</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6194</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.9032</v>
+        <v>-10.968</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.3868</v>
+        <v>-14.4516</v>
       </c>
       <c r="F13" t="n">
-        <v>3.483600000000001</v>
+        <v>3.4836</v>
       </c>
       <c r="G13" t="n">
         <v>-12.4008</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.753199999999999</v>
+        <v>-3.7532</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.647400000000001</v>
+        <v>-8.647399999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-3.0787</v>
@@ -1447,7 +1447,7 @@
         <v>-2.2358</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8427000000000003</v>
+        <v>-0.8427000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-9.322000000000001</v>
@@ -1459,7 +1459,7 @@
         <v>-7.804799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.975700000000001</v>
+        <v>2.9757</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.8626</v>
@@ -1468,16 +1468,16 @@
         <v>19.8384</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.927</v>
+        <v>-0.9919</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2276999999999998</v>
+        <v>1.1628</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1548</v>
+        <v>-2.1549</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5508999999999995</v>
       </c>
       <c r="W13" t="n">
         <v>4.3271</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.1745</v>
+        <v>11.1598</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5856</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5889</v>
+        <v>3.1457</v>
       </c>
       <c r="G14" t="n">
         <v>9.815899999999999</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9867</v>
+        <v>-0.0014</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2469</v>
+        <v>0.1815</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7398</v>
+        <v>-0.1829</v>
       </c>
       <c r="V14" t="n">
         <v>1.5437</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5444</v>
+        <v>3.9943</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4786</v>
+        <v>1.7644</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0658</v>
+        <v>2.2299</v>
       </c>
       <c r="G15" t="n">
         <v>2.1775</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2317</v>
+        <v>0.6816</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9297</v>
+        <v>0.2155</v>
       </c>
       <c r="U15" t="n">
-        <v>0.302</v>
+        <v>0.4661</v>
       </c>
       <c r="V15" t="n">
         <v>1.1352</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2037</v>
+        <v>2.7051</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9206</v>
+        <v>-0.0098</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2831</v>
+        <v>2.7149</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6889999999999999</v>
+        <v>3.2365</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7317</v>
+        <v>-0.0206</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0427</v>
+        <v>3.257</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5779</v>
+        <v>2.6711</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3745</v>
+        <v>0.1008</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2034</v>
+        <v>2.5703</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1111</v>
+        <v>0.5653</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3572</v>
+        <v>-0.1214</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2461</v>
+        <v>0.6867</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1822</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1661</v>
+        <v>-2.9758</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>6.3002</v>
+        <v>0.0439</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5801</v>
+        <v>0.2948</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7201</v>
+        <v>-0.2509</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6032</v>
+        <v>1.0118</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.532</v>
+        <v>1.0118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6311</v>
+        <v>0.7476</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1118</v>
+        <v>-1.8342</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7429</v>
+        <v>2.5817</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2365</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0206</v>
+        <v>0.7317</v>
       </c>
       <c r="I17" t="n">
-        <v>3.257</v>
+        <v>-0.0427</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6711</v>
+        <v>0.5779</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1008</v>
+        <v>0.3745</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5703</v>
+        <v>0.2034</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5653</v>
+        <v>0.1111</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1214</v>
+        <v>0.3572</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6867</v>
+        <v>-0.2461</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5871</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9758</v>
+        <v>-4.1661</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0301</v>
+        <v>2.844</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1928</v>
+        <v>1.8253</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2228</v>
+        <v>1.0187</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0118</v>
+        <v>-0.6032</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X17" t="n">
-        <v>1.0118</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0184</v>
+        <v>0.1162</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4898</v>
+        <v>-2.3878</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5082</v>
+        <v>2.504</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0444</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5243</v>
+        <v>-0.4265</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1303</v>
+        <v>-0.0283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.394</v>
+        <v>-0.3983</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9929</v>
+        <v>-0.4385</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9035</v>
+        <v>-1.5974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9106</v>
+        <v>1.1588</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5915</v>
@@ -1936,13 +1936,13 @@
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8694</v>
+        <v>-1.315</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.4421</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1212</v>
+        <v>-0.873</v>
       </c>
       <c r="V19" t="n">
         <v>0.6745</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2521</v>
+        <v>-0.4952</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1891</v>
+        <v>-2.0606</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.063</v>
+        <v>1.5654</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1526</v>
+        <v>1.4712</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3831</v>
+        <v>-0.8219</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7696</v>
+        <v>2.2932</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6199</v>
+        <v>0.3325</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0202</v>
+        <v>-1.7986</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>2.1311</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>1.1387</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4032</v>
+        <v>0.9767</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1295</v>
+        <v>0.162</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.1661</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3135</v>
+        <v>0.7595</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4308</v>
+        <v>0.3006</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1173</v>
+        <v>0.459</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2065</v>
+        <v>-0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5129</v>
+        <v>-1.2187</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.203</v>
+        <v>-1.101</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3099</v>
+        <v>-0.1178</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4224</v>
@@ -2092,13 +2092,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0906</v>
+        <v>-0.7964</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3117</v>
+        <v>-0.2097</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7788</v>
+        <v>-0.5867</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7501</v>
+        <v>-1.6322</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9789</v>
+        <v>-0.5972</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2287</v>
+        <v>-1.035</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4712</v>
+        <v>-1.1526</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8219</v>
+        <v>-0.3831</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2932</v>
+        <v>-0.7696</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3325</v>
+        <v>-0.6199</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7986</v>
+        <v>0.0202</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1311</v>
+        <v>-0.64</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1387</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9767</v>
+        <v>-0.4032</v>
       </c>
       <c r="O22" t="n">
-        <v>0.162</v>
+        <v>-0.1295</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1661</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4954</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6177</v>
+        <v>0.0227</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1223</v>
+        <v>-0.0893</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1609</v>
+        <v>-2.3549</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5924</v>
+        <v>-3.6741</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4314</v>
+        <v>1.3192</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7784</v>
@@ -2248,13 +2248,13 @@
         <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.8842</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9238</v>
+        <v>-0.0056</v>
       </c>
       <c r="U23" t="n">
-        <v>1.002</v>
+        <v>0.8898</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0639</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.9032</v>
+        <v>12.5835</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4837</v>
+        <v>-3.483700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>15.3867</v>
+        <v>16.0668</v>
       </c>
       <c r="G24" t="n">
         <v>12.4008</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7532</v>
+        <v>3.753200000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>8.647600000000001</v>
+        <v>8.647599999999999</v>
       </c>
       <c r="J24" t="n">
         <v>9.321900000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5173</v>
+        <v>1.517300000000001</v>
       </c>
       <c r="L24" t="n">
         <v>7.804799999999999</v>
@@ -2314,7 +2314,7 @@
         <v>2.236</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8425999999999998</v>
+        <v>0.8426</v>
       </c>
       <c r="P24" t="n">
         <v>-2.9759</v>
@@ -2326,16 +2326,16 @@
         <v>16.8626</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9271</v>
+        <v>2.6073</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1549</v>
+        <v>2.1547</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2275</v>
+        <v>0.4525</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5511000000000001</v>
+        <v>0.5511000000000004</v>
       </c>
       <c r="W24" t="n">
         <v>4.878</v>
